--- a/NejcDolinar/Opravljeno Delo/DolinarNejc.xlsx
+++ b/NejcDolinar/Opravljeno Delo/DolinarNejc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nejc\Desktop\Test\alma2026racunalnistvoOblak\NejcDolinar\Opravljeno Delo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BD52288E-4C12-4BAA-A4C1-54088448EC32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B4674500-B099-4F3F-ACF2-B143EB7C488F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -430,7 +430,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -452,12 +452,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -714,7 +708,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
